--- a/record.xlsx
+++ b/record.xlsx
@@ -3,16 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D00F0806-389A-4CF8-99E5-0C4B937A2101}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D639DB4-CF2D-4B59-9EB9-280AD05F4A35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="夥伴名單" sheetId="4" r:id="rId1"/>
     <sheet name="眷屬名單" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="171027"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -22,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3965" uniqueCount="1901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3966" uniqueCount="1901">
   <si>
     <t>id</t>
   </si>
@@ -53001,7 +53000,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F427"/>
+  <dimension ref="A1:G427"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" customWidth="1"/>
@@ -53009,9 +53008,10 @@
     <col min="3" max="3" width="26.140625" customWidth="1"/>
     <col min="4" max="4" width="23.42578125" customWidth="1"/>
     <col min="5" max="5" width="26.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -53030,8 +53030,11 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>1045</v>
       </c>
@@ -53051,7 +53054,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>1048</v>
       </c>
@@ -53071,7 +53074,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>1050</v>
       </c>
@@ -53091,7 +53094,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>1052</v>
       </c>
@@ -53111,7 +53114,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>1054</v>
       </c>
@@ -53131,7 +53134,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>1056</v>
       </c>
@@ -53151,7 +53154,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>1058</v>
       </c>
@@ -53171,7 +53174,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>1060</v>
       </c>
@@ -53191,7 +53194,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>1062</v>
       </c>
@@ -53211,7 +53214,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>1064</v>
       </c>
@@ -53231,7 +53234,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>1066</v>
       </c>
@@ -53251,7 +53254,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>1068</v>
       </c>
@@ -53271,7 +53274,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>1070</v>
       </c>
@@ -53291,7 +53294,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>1072</v>
       </c>
@@ -53311,7 +53314,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>1074</v>
       </c>
